--- a/www/flightdata/xlsx/eoss-351.xlsx
+++ b/www/flightdata/xlsx/eoss-351.xlsx
@@ -2631,7 +2631,7 @@
         <v>20454.52</v>
       </c>
       <c r="I2">
-        <v>416</v>
+        <v>302</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
